--- a/Acre_Key_Master_Map_Database.xlsx
+++ b/Acre_Key_Master_Map_Database.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I497"/>
+  <dimension ref="A1:I545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21308,7 +21308,7 @@
     <row r="485">
       <c r="A485" s="3" t="inlineStr">
         <is>
-          <t>AP08</t>
+          <t>AP04</t>
         </is>
       </c>
       <c r="B485" s="3" t="inlineStr">
@@ -21318,14 +21318,14 @@
       </c>
       <c r="C485" s="3" t="inlineStr">
         <is>
-          <t>Indiranagar</t>
+          <t>Richmond Town</t>
         </is>
       </c>
       <c r="D485" s="4" t="n">
-        <v>12.9784</v>
+        <v>12.9612</v>
       </c>
       <c r="E485" s="4" t="n">
-        <v>77.6408</v>
+        <v>77.60120000000001</v>
       </c>
       <c r="F485" s="3" t="inlineStr">
         <is>
@@ -21344,14 +21344,14 @@
       </c>
       <c r="I485" s="3" t="inlineStr">
         <is>
-          <t>Zone: East Bangalore | Avg Price: ₹17500/sqft | Range: ₹13000–24000/sqft | Category: Ultra-Luxury</t>
+          <t>Zone: Central Bangalore | Avg Price: ₹21500/sqft | Range: ₹16000–28000/sqft | Category: Ultra-Luxury</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="3" t="inlineStr">
         <is>
-          <t>AP10</t>
+          <t>AP05</t>
         </is>
       </c>
       <c r="B486" s="3" t="inlineStr">
@@ -21361,14 +21361,14 @@
       </c>
       <c r="C486" s="3" t="inlineStr">
         <is>
-          <t>Koramangala</t>
+          <t>Sadashivanagar</t>
         </is>
       </c>
       <c r="D486" s="4" t="n">
-        <v>12.9352</v>
+        <v>13.0082</v>
       </c>
       <c r="E486" s="4" t="n">
-        <v>77.6245</v>
+        <v>77.5812</v>
       </c>
       <c r="F486" s="3" t="inlineStr">
         <is>
@@ -21387,14 +21387,14 @@
       </c>
       <c r="I486" s="3" t="inlineStr">
         <is>
-          <t>Zone: East Bangalore | Avg Price: ₹16500/sqft | Range: ₹12000–23000/sqft | Category: Ultra-Luxury</t>
+          <t>Zone: Central Bangalore | Avg Price: ₹24000/sqft | Range: ₹18000–32000/sqft | Category: Ultra-Luxury</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="3" t="inlineStr">
         <is>
-          <t>AP21</t>
+          <t>AP06</t>
         </is>
       </c>
       <c r="B487" s="3" t="inlineStr">
@@ -21404,14 +21404,14 @@
       </c>
       <c r="C487" s="3" t="inlineStr">
         <is>
-          <t>Hebbal</t>
+          <t>Dollars Colony</t>
         </is>
       </c>
       <c r="D487" s="4" t="n">
-        <v>13.0358</v>
+        <v>13.0282</v>
       </c>
       <c r="E487" s="4" t="n">
-        <v>77.59699999999999</v>
+        <v>77.5782</v>
       </c>
       <c r="F487" s="3" t="inlineStr">
         <is>
@@ -21430,14 +21430,14 @@
       </c>
       <c r="I487" s="3" t="inlineStr">
         <is>
-          <t>Zone: North Bangalore | Avg Price: ₹11800/sqft | Range: ₹8500–17000/sqft | Category: Premium</t>
+          <t>Zone: North Bangalore | Avg Price: ₹18500/sqft | Range: ₹14000–25000/sqft | Category: Ultra-Luxury</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="3" t="inlineStr">
         <is>
-          <t>AP22</t>
+          <t>AP07</t>
         </is>
       </c>
       <c r="B488" s="3" t="inlineStr">
@@ -21447,14 +21447,14 @@
       </c>
       <c r="C488" s="3" t="inlineStr">
         <is>
-          <t>Bellandur</t>
+          <t>Sankey Road / Golf Course</t>
         </is>
       </c>
       <c r="D488" s="4" t="n">
-        <v>12.9304</v>
+        <v>12.9982</v>
       </c>
       <c r="E488" s="4" t="n">
-        <v>77.6784</v>
+        <v>77.5812</v>
       </c>
       <c r="F488" s="3" t="inlineStr">
         <is>
@@ -21473,14 +21473,14 @@
       </c>
       <c r="I488" s="3" t="inlineStr">
         <is>
-          <t>Zone: East Bangalore | Avg Price: ₹11500/sqft | Range: ₹8500–16000/sqft | Category: Premium</t>
+          <t>Zone: Central Bangalore | Avg Price: ₹26000/sqft | Range: ₹20000–35000/sqft | Category: Ultra-Luxury</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="3" t="inlineStr">
         <is>
-          <t>AP28</t>
+          <t>AP08</t>
         </is>
       </c>
       <c r="B489" s="3" t="inlineStr">
@@ -21490,14 +21490,14 @@
       </c>
       <c r="C489" s="3" t="inlineStr">
         <is>
-          <t>Whitefield</t>
+          <t>Indiranagar</t>
         </is>
       </c>
       <c r="D489" s="4" t="n">
-        <v>12.9698</v>
+        <v>12.9784</v>
       </c>
       <c r="E489" s="4" t="n">
-        <v>77.7499</v>
+        <v>77.6408</v>
       </c>
       <c r="F489" s="3" t="inlineStr">
         <is>
@@ -21516,14 +21516,14 @@
       </c>
       <c r="I489" s="3" t="inlineStr">
         <is>
-          <t>Zone: East Bangalore | Avg Price: ₹10500/sqft | Range: ₹7500–15000/sqft | Category: Premium</t>
+          <t>Zone: East Bangalore | Avg Price: ₹17500/sqft | Range: ₹13000–24000/sqft | Category: Ultra-Luxury</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="3" t="inlineStr">
         <is>
-          <t>AP30</t>
+          <t>AP09</t>
         </is>
       </c>
       <c r="B490" s="3" t="inlineStr">
@@ -21533,14 +21533,14 @@
       </c>
       <c r="C490" s="3" t="inlineStr">
         <is>
-          <t>Brookefield</t>
+          <t>Defence Colony Indiranagar</t>
         </is>
       </c>
       <c r="D490" s="4" t="n">
-        <v>12.9657</v>
+        <v>12.9721</v>
       </c>
       <c r="E490" s="4" t="n">
-        <v>77.71850000000001</v>
+        <v>77.6452</v>
       </c>
       <c r="F490" s="3" t="inlineStr">
         <is>
@@ -21559,14 +21559,14 @@
       </c>
       <c r="I490" s="3" t="inlineStr">
         <is>
-          <t>Zone: East Bangalore | Avg Price: ₹10200/sqft | Range: ₹7800–14000/sqft | Category: Premium</t>
+          <t>Zone: East Bangalore | Avg Price: ₹19000/sqft | Range: ₹14500–26000/sqft | Category: Ultra-Luxury</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="3" t="inlineStr">
         <is>
-          <t>AP38</t>
+          <t>AP10</t>
         </is>
       </c>
       <c r="B491" s="3" t="inlineStr">
@@ -21576,14 +21576,14 @@
       </c>
       <c r="C491" s="3" t="inlineStr">
         <is>
-          <t>Sarjapur Road</t>
+          <t>Koramangala</t>
         </is>
       </c>
       <c r="D491" s="4" t="n">
-        <v>12.9087</v>
+        <v>12.9352</v>
       </c>
       <c r="E491" s="4" t="n">
-        <v>77.6871</v>
+        <v>77.6245</v>
       </c>
       <c r="F491" s="3" t="inlineStr">
         <is>
@@ -21602,14 +21602,14 @@
       </c>
       <c r="I491" s="3" t="inlineStr">
         <is>
-          <t>Zone: East Bangalore | Avg Price: ₹9500/sqft | Range: ₹6800–13500/sqft | Category: Mid-Segment</t>
+          <t>Zone: East Bangalore | Avg Price: ₹16500/sqft | Range: ₹12000–23000/sqft | Category: Ultra-Luxury</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="3" t="inlineStr">
         <is>
-          <t>AP40</t>
+          <t>AP11</t>
         </is>
       </c>
       <c r="B492" s="3" t="inlineStr">
@@ -21619,14 +21619,14 @@
       </c>
       <c r="C492" s="3" t="inlineStr">
         <is>
-          <t>Marathahalli</t>
+          <t>Koramangala 3rd &amp; 4th Block</t>
         </is>
       </c>
       <c r="D492" s="4" t="n">
-        <v>12.9592</v>
+        <v>12.9341</v>
       </c>
       <c r="E492" s="4" t="n">
-        <v>77.6974</v>
+        <v>77.6251</v>
       </c>
       <c r="F492" s="3" t="inlineStr">
         <is>
@@ -21645,14 +21645,14 @@
       </c>
       <c r="I492" s="3" t="inlineStr">
         <is>
-          <t>Zone: East Bangalore | Avg Price: ₹9200/sqft | Range: ₹6800–12500/sqft | Category: Mid-Segment</t>
+          <t>Zone: East Bangalore | Avg Price: ₹18000/sqft | Range: ₹13500–25000/sqft | Category: Ultra-Luxury</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="3" t="inlineStr">
         <is>
-          <t>AP47</t>
+          <t>AP12</t>
         </is>
       </c>
       <c r="B493" s="3" t="inlineStr">
@@ -21662,14 +21662,14 @@
       </c>
       <c r="C493" s="3" t="inlineStr">
         <is>
-          <t>Mahadevapura</t>
+          <t>Ulsoor / Cambridge Layout</t>
         </is>
       </c>
       <c r="D493" s="4" t="n">
-        <v>12.9902</v>
+        <v>12.9752</v>
       </c>
       <c r="E493" s="4" t="n">
-        <v>77.6953</v>
+        <v>77.62520000000001</v>
       </c>
       <c r="F493" s="3" t="inlineStr">
         <is>
@@ -21688,14 +21688,14 @@
       </c>
       <c r="I493" s="3" t="inlineStr">
         <is>
-          <t>Zone: East Bangalore | Avg Price: ₹8500/sqft | Range: ₹6200–11800/sqft | Category: Mid-Segment</t>
+          <t>Zone: East Bangalore | Avg Price: ₹15500/sqft | Range: ₹11500–21000/sqft | Category: Premium</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="3" t="inlineStr">
         <is>
-          <t>AP52</t>
+          <t>AP13</t>
         </is>
       </c>
       <c r="B494" s="3" t="inlineStr">
@@ -21705,14 +21705,14 @@
       </c>
       <c r="C494" s="3" t="inlineStr">
         <is>
-          <t>Varthur</t>
+          <t>Benson Town</t>
         </is>
       </c>
       <c r="D494" s="4" t="n">
-        <v>12.9406</v>
+        <v>13.0012</v>
       </c>
       <c r="E494" s="4" t="n">
-        <v>77.7469</v>
+        <v>77.59820000000001</v>
       </c>
       <c r="F494" s="3" t="inlineStr">
         <is>
@@ -21731,14 +21731,14 @@
       </c>
       <c r="I494" s="3" t="inlineStr">
         <is>
-          <t>Zone: East Bangalore | Avg Price: ₹8200/sqft | Range: ₹6000–11500/sqft | Category: Mid-Segment</t>
+          <t>Zone: Central Bangalore | Avg Price: ₹15000/sqft | Range: ₹11000–20000/sqft | Category: Premium</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="3" t="inlineStr">
         <is>
-          <t>AP56</t>
+          <t>AP14</t>
         </is>
       </c>
       <c r="B495" s="3" t="inlineStr">
@@ -21748,14 +21748,14 @@
       </c>
       <c r="C495" s="3" t="inlineStr">
         <is>
-          <t>Budigere Cross</t>
+          <t>Frazer Town / Pulakeshinagar</t>
         </is>
       </c>
       <c r="D495" s="4" t="n">
-        <v>13.0673</v>
+        <v>12.9982</v>
       </c>
       <c r="E495" s="4" t="n">
-        <v>77.7423</v>
+        <v>77.6082</v>
       </c>
       <c r="F495" s="3" t="inlineStr">
         <is>
@@ -21774,14 +21774,14 @@
       </c>
       <c r="I495" s="3" t="inlineStr">
         <is>
-          <t>Zone: East Bangalore | Avg Price: ₹7500/sqft | Range: ₹5600–10200/sqft | Category: Mid-Segment</t>
+          <t>Zone: Central Bangalore | Avg Price: ₹14500/sqft | Range: ₹10500–19500/sqft | Category: Premium</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="3" t="inlineStr">
         <is>
-          <t>AP63</t>
+          <t>AP15</t>
         </is>
       </c>
       <c r="B496" s="3" t="inlineStr">
@@ -21791,14 +21791,14 @@
       </c>
       <c r="C496" s="3" t="inlineStr">
         <is>
-          <t>KR Puram</t>
+          <t>Cooke Town</t>
         </is>
       </c>
       <c r="D496" s="4" t="n">
-        <v>13.0075</v>
+        <v>13.0012</v>
       </c>
       <c r="E496" s="4" t="n">
-        <v>77.69589999999999</v>
+        <v>77.6182</v>
       </c>
       <c r="F496" s="3" t="inlineStr">
         <is>
@@ -21817,48 +21817,2112 @@
       </c>
       <c r="I496" s="3" t="inlineStr">
         <is>
-          <t>Zone: East Bangalore | Avg Price: ₹6800/sqft | Range: ₹4800–9200/sqft | Category: Budget</t>
+          <t>Zone: Central Bangalore | Avg Price: ₹14000/sqft | Range: ₹10000–19000/sqft | Category: Premium</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="3" t="inlineStr">
         <is>
+          <t>AP16</t>
+        </is>
+      </c>
+      <c r="B497" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C497" s="3" t="inlineStr">
+        <is>
+          <t>Vasanthnagar</t>
+        </is>
+      </c>
+      <c r="D497" s="4" t="n">
+        <v>12.9912</v>
+      </c>
+      <c r="E497" s="4" t="n">
+        <v>77.5882</v>
+      </c>
+      <c r="F497" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G497" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H497" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I497" s="3" t="inlineStr">
+        <is>
+          <t>Zone: Central Bangalore | Avg Price: ₹19500/sqft | Range: ₹14500–26000/sqft | Category: Ultra-Luxury</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="3" t="inlineStr">
+        <is>
+          <t>AP17</t>
+        </is>
+      </c>
+      <c r="B498" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C498" s="3" t="inlineStr">
+        <is>
+          <t>Cunningham Road</t>
+        </is>
+      </c>
+      <c r="D498" s="4" t="n">
+        <v>12.9882</v>
+      </c>
+      <c r="E498" s="4" t="n">
+        <v>77.59520000000001</v>
+      </c>
+      <c r="F498" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G498" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H498" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I498" s="3" t="inlineStr">
+        <is>
+          <t>Zone: Central Bangalore | Avg Price: ₹21000/sqft | Range: ₹15500–28000/sqft | Category: Ultra-Luxury</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="3" t="inlineStr">
+        <is>
+          <t>AP18</t>
+        </is>
+      </c>
+      <c r="B499" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C499" s="3" t="inlineStr">
+        <is>
+          <t>Palace Road</t>
+        </is>
+      </c>
+      <c r="D499" s="4" t="n">
+        <v>12.9882</v>
+      </c>
+      <c r="E499" s="4" t="n">
+        <v>77.5852</v>
+      </c>
+      <c r="F499" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G499" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H499" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I499" s="3" t="inlineStr">
+        <is>
+          <t>Zone: Central Bangalore | Avg Price: ₹20000/sqft | Range: ₹15000–27000/sqft | Category: Ultra-Luxury</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="3" t="inlineStr">
+        <is>
+          <t>AP19</t>
+        </is>
+      </c>
+      <c r="B500" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C500" s="3" t="inlineStr">
+        <is>
+          <t>Malleshwaram</t>
+        </is>
+      </c>
+      <c r="D500" s="4" t="n">
+        <v>12.9982</v>
+      </c>
+      <c r="E500" s="4" t="n">
+        <v>77.5682</v>
+      </c>
+      <c r="F500" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G500" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H500" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I500" s="3" t="inlineStr">
+        <is>
+          <t>Zone: West Bangalore | Avg Price: ₹15500/sqft | Range: ₹11500–21000/sqft | Category: Premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="3" t="inlineStr">
+        <is>
+          <t>AP20</t>
+        </is>
+      </c>
+      <c r="B501" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C501" s="3" t="inlineStr">
+        <is>
+          <t>Rajajinagar</t>
+        </is>
+      </c>
+      <c r="D501" s="4" t="n">
+        <v>12.9912</v>
+      </c>
+      <c r="E501" s="4" t="n">
+        <v>77.5532</v>
+      </c>
+      <c r="F501" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G501" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H501" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I501" s="3" t="inlineStr">
+        <is>
+          <t>Zone: West Bangalore | Avg Price: ₹13500/sqft | Range: ₹10000–18500/sqft | Category: Premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="3" t="inlineStr">
+        <is>
+          <t>AP21</t>
+        </is>
+      </c>
+      <c r="B502" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C502" s="3" t="inlineStr">
+        <is>
+          <t>Hebbal</t>
+        </is>
+      </c>
+      <c r="D502" s="4" t="n">
+        <v>13.0358</v>
+      </c>
+      <c r="E502" s="4" t="n">
+        <v>77.59699999999999</v>
+      </c>
+      <c r="F502" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G502" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H502" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I502" s="3" t="inlineStr">
+        <is>
+          <t>Zone: North Bangalore | Avg Price: ₹11800/sqft | Range: ₹8500–17000/sqft | Category: Premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="3" t="inlineStr">
+        <is>
+          <t>AP22</t>
+        </is>
+      </c>
+      <c r="B503" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C503" s="3" t="inlineStr">
+        <is>
+          <t>Bellandur</t>
+        </is>
+      </c>
+      <c r="D503" s="4" t="n">
+        <v>12.9304</v>
+      </c>
+      <c r="E503" s="4" t="n">
+        <v>77.6784</v>
+      </c>
+      <c r="F503" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G503" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H503" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I503" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹11500/sqft | Range: ₹8500–16000/sqft | Category: Premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="3" t="inlineStr">
+        <is>
+          <t>AP23</t>
+        </is>
+      </c>
+      <c r="B504" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C504" s="3" t="inlineStr">
+        <is>
+          <t>Devarabesanahalli / ORR</t>
+        </is>
+      </c>
+      <c r="D504" s="4" t="n">
+        <v>12.9298</v>
+      </c>
+      <c r="E504" s="4" t="n">
+        <v>77.6862</v>
+      </c>
+      <c r="F504" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G504" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H504" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I504" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹12200/sqft | Range: ₹9000–16500/sqft | Category: Premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="3" t="inlineStr">
+        <is>
+          <t>AP24</t>
+        </is>
+      </c>
+      <c r="B505" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C505" s="3" t="inlineStr">
+        <is>
+          <t>Kadubeesanahalli / ORR</t>
+        </is>
+      </c>
+      <c r="D505" s="4" t="n">
+        <v>12.9366</v>
+      </c>
+      <c r="E505" s="4" t="n">
+        <v>77.69199999999999</v>
+      </c>
+      <c r="F505" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G505" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H505" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I505" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹12000/sqft | Range: ₹8800–16200/sqft | Category: Premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="3" t="inlineStr">
+        <is>
+          <t>AP25</t>
+        </is>
+      </c>
+      <c r="B506" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C506" s="3" t="inlineStr">
+        <is>
+          <t>Marathahalli - Sarjapur ORR</t>
+        </is>
+      </c>
+      <c r="D506" s="4" t="n">
+        <v>12.9305</v>
+      </c>
+      <c r="E506" s="4" t="n">
+        <v>77.6874</v>
+      </c>
+      <c r="F506" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G506" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H506" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I506" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹11800/sqft | Range: ₹8600–16000/sqft | Category: Premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="3" t="inlineStr">
+        <is>
+          <t>AP26</t>
+        </is>
+      </c>
+      <c r="B507" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C507" s="3" t="inlineStr">
+        <is>
+          <t>HSR Layout</t>
+        </is>
+      </c>
+      <c r="D507" s="4" t="n">
+        <v>12.9121</v>
+      </c>
+      <c r="E507" s="4" t="n">
+        <v>77.64449999999999</v>
+      </c>
+      <c r="F507" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G507" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H507" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I507" s="3" t="inlineStr">
+        <is>
+          <t>Zone: South Bangalore | Avg Price: ₹13000/sqft | Range: ₹9500–17500/sqft | Category: Premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="3" t="inlineStr">
+        <is>
+          <t>AP27</t>
+        </is>
+      </c>
+      <c r="B508" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C508" s="3" t="inlineStr">
+        <is>
+          <t>Jayanagar</t>
+        </is>
+      </c>
+      <c r="D508" s="4" t="n">
+        <v>12.9282</v>
+      </c>
+      <c r="E508" s="4" t="n">
+        <v>77.58320000000001</v>
+      </c>
+      <c r="F508" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G508" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H508" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I508" s="3" t="inlineStr">
+        <is>
+          <t>Zone: South Bangalore | Avg Price: ₹14000/sqft | Range: ₹10200–19000/sqft | Category: Premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="3" t="inlineStr">
+        <is>
+          <t>AP28</t>
+        </is>
+      </c>
+      <c r="B509" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C509" s="3" t="inlineStr">
+        <is>
+          <t>Whitefield</t>
+        </is>
+      </c>
+      <c r="D509" s="4" t="n">
+        <v>12.9698</v>
+      </c>
+      <c r="E509" s="4" t="n">
+        <v>77.7499</v>
+      </c>
+      <c r="F509" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G509" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H509" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I509" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹10500/sqft | Range: ₹7500–15000/sqft | Category: Premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="3" t="inlineStr">
+        <is>
+          <t>AP29</t>
+        </is>
+      </c>
+      <c r="B510" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C510" s="3" t="inlineStr">
+        <is>
+          <t>EPIP Zone Whitefield</t>
+        </is>
+      </c>
+      <c r="D510" s="4" t="n">
+        <v>12.9758</v>
+      </c>
+      <c r="E510" s="4" t="n">
+        <v>77.7248</v>
+      </c>
+      <c r="F510" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G510" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H510" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I510" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹11200/sqft | Range: ₹8200–15500/sqft | Category: Premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="3" t="inlineStr">
+        <is>
+          <t>AP30</t>
+        </is>
+      </c>
+      <c r="B511" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C511" s="3" t="inlineStr">
+        <is>
+          <t>Brookefield</t>
+        </is>
+      </c>
+      <c r="D511" s="4" t="n">
+        <v>12.9657</v>
+      </c>
+      <c r="E511" s="4" t="n">
+        <v>77.71850000000001</v>
+      </c>
+      <c r="F511" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G511" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H511" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I511" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹10200/sqft | Range: ₹7800–14000/sqft | Category: Premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="3" t="inlineStr">
+        <is>
+          <t>AP31</t>
+        </is>
+      </c>
+      <c r="B512" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C512" s="3" t="inlineStr">
+        <is>
+          <t>Kundalahalli</t>
+        </is>
+      </c>
+      <c r="D512" s="4" t="n">
+        <v>12.9658</v>
+      </c>
+      <c r="E512" s="4" t="n">
+        <v>77.7115</v>
+      </c>
+      <c r="F512" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G512" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H512" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I512" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹10000/sqft | Range: ₹7500–13800/sqft | Category: Premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="3" t="inlineStr">
+        <is>
+          <t>AP32</t>
+        </is>
+      </c>
+      <c r="B513" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C513" s="3" t="inlineStr">
+        <is>
+          <t>Siddapura / Nallurhalli</t>
+        </is>
+      </c>
+      <c r="D513" s="4" t="n">
+        <v>12.9619</v>
+      </c>
+      <c r="E513" s="4" t="n">
+        <v>77.7291</v>
+      </c>
+      <c r="F513" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G513" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H513" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I513" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹9800/sqft | Range: ₹7200–13500/sqft | Category: Premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="3" t="inlineStr">
+        <is>
+          <t>AP33</t>
+        </is>
+      </c>
+      <c r="B514" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C514" s="3" t="inlineStr">
+        <is>
+          <t>ECC Road Whitefield</t>
+        </is>
+      </c>
+      <c r="D514" s="4" t="n">
+        <v>12.978</v>
+      </c>
+      <c r="E514" s="4" t="n">
+        <v>77.73779999999999</v>
+      </c>
+      <c r="F514" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G514" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H514" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I514" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹11000/sqft | Range: ₹8000–15200/sqft | Category: Premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="3" t="inlineStr">
+        <is>
+          <t>AP34</t>
+        </is>
+      </c>
+      <c r="B515" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C515" s="3" t="inlineStr">
+        <is>
+          <t>Hope Farm Junction</t>
+        </is>
+      </c>
+      <c r="D515" s="4" t="n">
+        <v>12.9858</v>
+      </c>
+      <c r="E515" s="4" t="n">
+        <v>77.74890000000001</v>
+      </c>
+      <c r="F515" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G515" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H515" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I515" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹10400/sqft | Range: ₹7600–14500/sqft | Category: Premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="3" t="inlineStr">
+        <is>
+          <t>AP35</t>
+        </is>
+      </c>
+      <c r="B516" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C516" s="3" t="inlineStr">
+        <is>
+          <t>Pattandur Agrahara</t>
+        </is>
+      </c>
+      <c r="D516" s="4" t="n">
+        <v>12.9873</v>
+      </c>
+      <c r="E516" s="4" t="n">
+        <v>77.7531</v>
+      </c>
+      <c r="F516" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G516" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H516" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I516" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹10200/sqft | Range: ₹7500–14200/sqft | Category: Premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="3" t="inlineStr">
+        <is>
+          <t>AP36</t>
+        </is>
+      </c>
+      <c r="B517" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C517" s="3" t="inlineStr">
+        <is>
+          <t>Kadugodi</t>
+        </is>
+      </c>
+      <c r="D517" s="4" t="n">
+        <v>12.9892</v>
+      </c>
+      <c r="E517" s="4" t="n">
+        <v>77.7508</v>
+      </c>
+      <c r="F517" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G517" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H517" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I517" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹9500/sqft | Range: ₹7000–13000/sqft | Category: Mid-Segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="3" t="inlineStr">
+        <is>
+          <t>AP37</t>
+        </is>
+      </c>
+      <c r="B518" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C518" s="3" t="inlineStr">
+        <is>
+          <t>Belathur</t>
+        </is>
+      </c>
+      <c r="D518" s="4" t="n">
+        <v>13.0117</v>
+      </c>
+      <c r="E518" s="4" t="n">
+        <v>77.74590000000001</v>
+      </c>
+      <c r="F518" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G518" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H518" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I518" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹8800/sqft | Range: ₹6500–12200/sqft | Category: Mid-Segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="3" t="inlineStr">
+        <is>
+          <t>AP38</t>
+        </is>
+      </c>
+      <c r="B519" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C519" s="3" t="inlineStr">
+        <is>
+          <t>Sarjapur Road</t>
+        </is>
+      </c>
+      <c r="D519" s="4" t="n">
+        <v>12.9087</v>
+      </c>
+      <c r="E519" s="4" t="n">
+        <v>77.6871</v>
+      </c>
+      <c r="F519" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G519" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H519" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I519" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹9500/sqft | Range: ₹6800–13500/sqft | Category: Mid-Segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="3" t="inlineStr">
+        <is>
+          <t>AP39</t>
+        </is>
+      </c>
+      <c r="B520" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C520" s="3" t="inlineStr">
+        <is>
+          <t>Doddakannelli / Haralur</t>
+        </is>
+      </c>
+      <c r="D520" s="4" t="n">
+        <v>12.9094</v>
+      </c>
+      <c r="E520" s="4" t="n">
+        <v>77.6978</v>
+      </c>
+      <c r="F520" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G520" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H520" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I520" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹9800/sqft | Range: ₹7000–13800/sqft | Category: Mid-Segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="3" t="inlineStr">
+        <is>
+          <t>AP40</t>
+        </is>
+      </c>
+      <c r="B521" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C521" s="3" t="inlineStr">
+        <is>
+          <t>Marathahalli</t>
+        </is>
+      </c>
+      <c r="D521" s="4" t="n">
+        <v>12.9592</v>
+      </c>
+      <c r="E521" s="4" t="n">
+        <v>77.6974</v>
+      </c>
+      <c r="F521" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G521" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H521" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I521" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹9200/sqft | Range: ₹6800–12500/sqft | Category: Mid-Segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="3" t="inlineStr">
+        <is>
+          <t>AP41</t>
+        </is>
+      </c>
+      <c r="B522" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C522" s="3" t="inlineStr">
+        <is>
+          <t>Doddanekundi</t>
+        </is>
+      </c>
+      <c r="D522" s="4" t="n">
+        <v>12.9728</v>
+      </c>
+      <c r="E522" s="4" t="n">
+        <v>77.6961</v>
+      </c>
+      <c r="F522" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G522" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H522" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I522" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹9000/sqft | Range: ₹6600–12200/sqft | Category: Mid-Segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="3" t="inlineStr">
+        <is>
+          <t>AP42</t>
+        </is>
+      </c>
+      <c r="B523" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C523" s="3" t="inlineStr">
+        <is>
+          <t>Panathur</t>
+        </is>
+      </c>
+      <c r="D523" s="4" t="n">
+        <v>12.9348</v>
+      </c>
+      <c r="E523" s="4" t="n">
+        <v>77.71210000000001</v>
+      </c>
+      <c r="F523" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G523" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H523" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I523" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹8900/sqft | Range: ₹6500–12000/sqft | Category: Mid-Segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="3" t="inlineStr">
+        <is>
+          <t>AP43</t>
+        </is>
+      </c>
+      <c r="B524" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C524" s="3" t="inlineStr">
+        <is>
+          <t>Balagere</t>
+        </is>
+      </c>
+      <c r="D524" s="4" t="n">
+        <v>12.9308</v>
+      </c>
+      <c r="E524" s="4" t="n">
+        <v>77.7192</v>
+      </c>
+      <c r="F524" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G524" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H524" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I524" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹8400/sqft | Range: ₹6200–11500/sqft | Category: Mid-Segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="3" t="inlineStr">
+        <is>
+          <t>AP44</t>
+        </is>
+      </c>
+      <c r="B525" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C525" s="3" t="inlineStr">
+        <is>
+          <t>Gunjur</t>
+        </is>
+      </c>
+      <c r="D525" s="4" t="n">
+        <v>12.9288</v>
+      </c>
+      <c r="E525" s="4" t="n">
+        <v>77.74509999999999</v>
+      </c>
+      <c r="F525" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G525" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H525" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I525" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹8100/sqft | Range: ₹6000–11200/sqft | Category: Mid-Segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="3" t="inlineStr">
+        <is>
+          <t>AP45</t>
+        </is>
+      </c>
+      <c r="B526" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C526" s="3" t="inlineStr">
+        <is>
+          <t>Soukya Road</t>
+        </is>
+      </c>
+      <c r="D526" s="4" t="n">
+        <v>12.9621</v>
+      </c>
+      <c r="E526" s="4" t="n">
+        <v>77.7698</v>
+      </c>
+      <c r="F526" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G526" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H526" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I526" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹7800/sqft | Range: ₹5800–10800/sqft | Category: Mid-Segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="3" t="inlineStr">
+        <is>
+          <t>AP46</t>
+        </is>
+      </c>
+      <c r="B527" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C527" s="3" t="inlineStr">
+        <is>
+          <t>Seetharamapalya</t>
+        </is>
+      </c>
+      <c r="D527" s="4" t="n">
+        <v>12.9781</v>
+      </c>
+      <c r="E527" s="4" t="n">
+        <v>77.7058</v>
+      </c>
+      <c r="F527" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G527" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H527" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I527" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹8900/sqft | Range: ₹6500–12000/sqft | Category: Mid-Segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="3" t="inlineStr">
+        <is>
+          <t>AP47</t>
+        </is>
+      </c>
+      <c r="B528" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C528" s="3" t="inlineStr">
+        <is>
+          <t>Mahadevapura</t>
+        </is>
+      </c>
+      <c r="D528" s="4" t="n">
+        <v>12.9902</v>
+      </c>
+      <c r="E528" s="4" t="n">
+        <v>77.6953</v>
+      </c>
+      <c r="F528" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G528" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H528" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I528" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹8500/sqft | Range: ₹6200–11800/sqft | Category: Mid-Segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="3" t="inlineStr">
+        <is>
+          <t>AP48</t>
+        </is>
+      </c>
+      <c r="B529" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C529" s="3" t="inlineStr">
+        <is>
+          <t>Hoodi</t>
+        </is>
+      </c>
+      <c r="D529" s="4" t="n">
+        <v>12.9868</v>
+      </c>
+      <c r="E529" s="4" t="n">
+        <v>77.7011</v>
+      </c>
+      <c r="F529" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G529" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H529" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I529" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹8700/sqft | Range: ₹6400–11900/sqft | Category: Mid-Segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="3" t="inlineStr">
+        <is>
+          <t>AP49</t>
+        </is>
+      </c>
+      <c r="B530" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C530" s="3" t="inlineStr">
+        <is>
+          <t>Garudacharpalya</t>
+        </is>
+      </c>
+      <c r="D530" s="4" t="n">
+        <v>12.9904</v>
+      </c>
+      <c r="E530" s="4" t="n">
+        <v>77.6961</v>
+      </c>
+      <c r="F530" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G530" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H530" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I530" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹8400/sqft | Range: ₹6100–11500/sqft | Category: Mid-Segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="3" t="inlineStr">
+        <is>
+          <t>AP50</t>
+        </is>
+      </c>
+      <c r="B531" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C531" s="3" t="inlineStr">
+        <is>
+          <t>Singayyanapalya</t>
+        </is>
+      </c>
+      <c r="D531" s="4" t="n">
+        <v>12.9912</v>
+      </c>
+      <c r="E531" s="4" t="n">
+        <v>77.6871</v>
+      </c>
+      <c r="F531" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G531" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H531" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I531" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹8300/sqft | Range: ₹6000–11400/sqft | Category: Mid-Segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="3" t="inlineStr">
+        <is>
+          <t>AP51</t>
+        </is>
+      </c>
+      <c r="B532" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C532" s="3" t="inlineStr">
+        <is>
+          <t>Varthur Junction</t>
+        </is>
+      </c>
+      <c r="D532" s="4" t="n">
+        <v>12.9535</v>
+      </c>
+      <c r="E532" s="4" t="n">
+        <v>77.74550000000001</v>
+      </c>
+      <c r="F532" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G532" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H532" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I532" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹8500/sqft | Range: ₹6200–11800/sqft | Category: Mid-Segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="3" t="inlineStr">
+        <is>
+          <t>AP52</t>
+        </is>
+      </c>
+      <c r="B533" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C533" s="3" t="inlineStr">
+        <is>
+          <t>Varthur</t>
+        </is>
+      </c>
+      <c r="D533" s="4" t="n">
+        <v>12.9406</v>
+      </c>
+      <c r="E533" s="4" t="n">
+        <v>77.7469</v>
+      </c>
+      <c r="F533" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G533" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H533" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I533" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹8200/sqft | Range: ₹6000–11500/sqft | Category: Mid-Segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="3" t="inlineStr">
+        <is>
+          <t>AP53</t>
+        </is>
+      </c>
+      <c r="B534" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C534" s="3" t="inlineStr">
+        <is>
+          <t>Varthur Lakefront</t>
+        </is>
+      </c>
+      <c r="D534" s="4" t="n">
+        <v>12.9421</v>
+      </c>
+      <c r="E534" s="4" t="n">
+        <v>77.74120000000001</v>
+      </c>
+      <c r="F534" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G534" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H534" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I534" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹8600/sqft | Range: ₹6300–11900/sqft | Category: Mid-Segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="3" t="inlineStr">
+        <is>
+          <t>AP54</t>
+        </is>
+      </c>
+      <c r="B535" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C535" s="3" t="inlineStr">
+        <is>
+          <t>Cheemasandra</t>
+        </is>
+      </c>
+      <c r="D535" s="4" t="n">
+        <v>13.0496</v>
+      </c>
+      <c r="E535" s="4" t="n">
+        <v>77.7475</v>
+      </c>
+      <c r="F535" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G535" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H535" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I535" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹7600/sqft | Range: ₹5600–10400/sqft | Category: Mid-Segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="3" t="inlineStr">
+        <is>
+          <t>AP55</t>
+        </is>
+      </c>
+      <c r="B536" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C536" s="3" t="inlineStr">
+        <is>
+          <t>Nimbekaipura</t>
+        </is>
+      </c>
+      <c r="D536" s="4" t="n">
+        <v>13.0561</v>
+      </c>
+      <c r="E536" s="4" t="n">
+        <v>77.7512</v>
+      </c>
+      <c r="F536" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G536" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H536" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I536" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹7400/sqft | Range: ₹5500–10000/sqft | Category: Mid-Segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="3" t="inlineStr">
+        <is>
+          <t>AP56</t>
+        </is>
+      </c>
+      <c r="B537" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C537" s="3" t="inlineStr">
+        <is>
+          <t>Budigere Cross</t>
+        </is>
+      </c>
+      <c r="D537" s="4" t="n">
+        <v>13.0673</v>
+      </c>
+      <c r="E537" s="4" t="n">
+        <v>77.7423</v>
+      </c>
+      <c r="F537" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G537" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H537" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I537" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹7500/sqft | Range: ₹5600–10200/sqft | Category: Mid-Segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="3" t="inlineStr">
+        <is>
+          <t>AP57</t>
+        </is>
+      </c>
+      <c r="B538" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C538" s="3" t="inlineStr">
+        <is>
+          <t>Budigere Main Road</t>
+        </is>
+      </c>
+      <c r="D538" s="4" t="n">
+        <v>13.0512</v>
+      </c>
+      <c r="E538" s="4" t="n">
+        <v>77.74809999999999</v>
+      </c>
+      <c r="F538" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G538" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H538" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I538" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹7300/sqft | Range: ₹5400–9900/sqft | Category: Mid-Segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="3" t="inlineStr">
+        <is>
+          <t>AP58</t>
+        </is>
+      </c>
+      <c r="B539" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C539" s="3" t="inlineStr">
+        <is>
+          <t>Mandur / Budigere</t>
+        </is>
+      </c>
+      <c r="D539" s="4" t="n">
+        <v>13.0712</v>
+      </c>
+      <c r="E539" s="4" t="n">
+        <v>77.7495</v>
+      </c>
+      <c r="F539" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G539" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H539" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I539" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹7100/sqft | Range: ₹5200–9600/sqft | Category: Mid-Segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="3" t="inlineStr">
+        <is>
+          <t>AP59</t>
+        </is>
+      </c>
+      <c r="B540" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C540" s="3" t="inlineStr">
+        <is>
+          <t>Hoskote Toll / OMR</t>
+        </is>
+      </c>
+      <c r="D540" s="4" t="n">
+        <v>13.0612</v>
+      </c>
+      <c r="E540" s="4" t="n">
+        <v>77.76819999999999</v>
+      </c>
+      <c r="F540" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G540" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H540" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I540" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹6900/sqft | Range: ₹5000–9400/sqft | Category: Budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="3" t="inlineStr">
+        <is>
+          <t>AP60</t>
+        </is>
+      </c>
+      <c r="B541" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C541" s="3" t="inlineStr">
+        <is>
+          <t>Aavalahalli</t>
+        </is>
+      </c>
+      <c r="D541" s="4" t="n">
+        <v>13.0231</v>
+      </c>
+      <c r="E541" s="4" t="n">
+        <v>77.7118</v>
+      </c>
+      <c r="F541" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G541" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H541" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I541" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹7000/sqft | Range: ₹5100–9500/sqft | Category: Budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="3" t="inlineStr">
+        <is>
+          <t>AP61</t>
+        </is>
+      </c>
+      <c r="B542" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C542" s="3" t="inlineStr">
+        <is>
+          <t>Battarahalli</t>
+        </is>
+      </c>
+      <c r="D542" s="4" t="n">
+        <v>13.0145</v>
+      </c>
+      <c r="E542" s="4" t="n">
+        <v>77.7012</v>
+      </c>
+      <c r="F542" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G542" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H542" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I542" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹7200/sqft | Range: ₹5300–9800/sqft | Category: Budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="3" t="inlineStr">
+        <is>
+          <t>AP62</t>
+        </is>
+      </c>
+      <c r="B543" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C543" s="3" t="inlineStr">
+        <is>
+          <t>Benniganahalli</t>
+        </is>
+      </c>
+      <c r="D543" s="4" t="n">
+        <v>12.9935</v>
+      </c>
+      <c r="E543" s="4" t="n">
+        <v>77.66200000000001</v>
+      </c>
+      <c r="F543" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G543" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H543" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I543" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹7800/sqft | Range: ₹5700–10500/sqft | Category: Mid-Segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="3" t="inlineStr">
+        <is>
+          <t>AP63</t>
+        </is>
+      </c>
+      <c r="B544" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Center</t>
+        </is>
+      </c>
+      <c r="C544" s="3" t="inlineStr">
+        <is>
+          <t>KR Puram</t>
+        </is>
+      </c>
+      <c r="D544" s="4" t="n">
+        <v>13.0075</v>
+      </c>
+      <c r="E544" s="4" t="n">
+        <v>77.69589999999999</v>
+      </c>
+      <c r="F544" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G544" s="3" t="inlineStr">
+        <is>
+          <t>Area Price Density Heatmap</t>
+        </is>
+      </c>
+      <c r="H544" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I544" s="3" t="inlineStr">
+        <is>
+          <t>Zone: East Bangalore | Avg Price: ₹6800/sqft | Range: ₹4800–9200/sqft | Category: Budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="3" t="inlineStr">
+        <is>
           <t>AP64</t>
         </is>
       </c>
-      <c r="B497" s="3" t="inlineStr">
+      <c r="B545" s="3" t="inlineStr">
         <is>
           <t>Area Price Center</t>
         </is>
       </c>
-      <c r="C497" s="3" t="inlineStr">
+      <c r="C545" s="3" t="inlineStr">
         <is>
           <t>Electronic City Phase 1</t>
         </is>
       </c>
-      <c r="D497" s="4" t="n">
+      <c r="D545" s="4" t="n">
         <v>12.8452</v>
       </c>
-      <c r="E497" s="4" t="n">
+      <c r="E545" s="4" t="n">
         <v>77.6602</v>
       </c>
-      <c r="F497" s="3" t="inlineStr">
-        <is>
-          <t>index.html</t>
-        </is>
-      </c>
-      <c r="G497" s="3" t="inlineStr">
+      <c r="F545" s="3" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G545" s="3" t="inlineStr">
         <is>
           <t>Area Price Density Heatmap</t>
         </is>
       </c>
-      <c r="H497" s="3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="I497" s="3" t="inlineStr">
+      <c r="H545" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I545" s="3" t="inlineStr">
         <is>
           <t>Zone: South Bangalore | Avg Price: ₹6800/sqft | Range: ₹5000–9200/sqft | Category: Budget</t>
         </is>
@@ -28833,13 +30897,13 @@
         </is>
       </c>
       <c r="E2" s="4" t="n">
-        <v>6800</v>
+        <v>7000</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>4800</v>
+        <v>5100</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>9200</v>
+        <v>9500</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
@@ -28850,10 +30914,10 @@
         <v>7</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>13.0075</v>
+        <v>13.0231</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>77.69589999999999</v>
+        <v>77.7118</v>
       </c>
     </row>
     <row r="3">
@@ -28878,10 +30942,10 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>8200</v>
+        <v>8400</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>6000</v>
+        <v>6200</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>11500</v>
@@ -28895,10 +30959,10 @@
         <v>6</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>12.9406</v>
+        <v>12.9308</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>77.7469</v>
+        <v>77.7192</v>
       </c>
     </row>
     <row r="4">
@@ -28923,13 +30987,13 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>6800</v>
+        <v>7200</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>4800</v>
+        <v>5300</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>9200</v>
+        <v>9800</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -28940,10 +31004,10 @@
         <v>7</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>13.0075</v>
+        <v>13.0145</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>77.69589999999999</v>
+        <v>77.7012</v>
       </c>
     </row>
     <row r="5">
@@ -29238,13 +31302,13 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>9500</v>
+        <v>7600</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>7000</v>
+        <v>5600</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>13500</v>
+        <v>10400</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
@@ -29255,10 +31319,10 @@
         <v>1</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>13.0512</v>
+        <v>13.0496</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>77.74809999999999</v>
+        <v>77.7475</v>
       </c>
     </row>
     <row r="12">
@@ -29283,13 +31347,13 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>9500</v>
+        <v>7600</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>7000</v>
+        <v>5600</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>13500</v>
+        <v>10400</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
@@ -29373,13 +31437,13 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>9500</v>
+        <v>8100</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>13500</v>
+        <v>11200</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
@@ -29418,13 +31482,13 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>9500</v>
+        <v>8700</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>7000</v>
+        <v>6400</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>13500</v>
+        <v>11900</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -29435,10 +31499,10 @@
         <v>0</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>12.9698</v>
+        <v>12.9868</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>77.7499</v>
+        <v>77.7011</v>
       </c>
     </row>
     <row r="16">
@@ -29508,17 +31572,17 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>9500</v>
+        <v>6900</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>7000</v>
+        <v>5000</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>13500</v>
+        <v>9400</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Mid-Segment</t>
+          <t>Budget</t>
         </is>
       </c>
       <c r="I17" s="4" t="n">
@@ -29739,7 +31803,7 @@
         <v>7000</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>13500</v>
+        <v>13000</v>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
@@ -29784,7 +31848,7 @@
         <v>7000</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>13500</v>
+        <v>13000</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
@@ -29868,13 +31932,13 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>9500</v>
+        <v>7400</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>7000</v>
+        <v>5500</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>13500</v>
+        <v>10000</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
@@ -29958,13 +32022,13 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>9500</v>
+        <v>8900</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>7000</v>
+        <v>6500</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>13500</v>
+        <v>12000</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
@@ -29975,10 +32039,10 @@
         <v>2</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>12.9391</v>
+        <v>12.9348</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>77.7377</v>
+        <v>77.71210000000001</v>
       </c>
     </row>
     <row r="28">
@@ -30003,13 +32067,13 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>8200</v>
+        <v>8900</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>6000</v>
+        <v>6500</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>11500</v>
+        <v>12000</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
@@ -30020,10 +32084,10 @@
         <v>6</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>12.9406</v>
+        <v>12.9348</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>77.7469</v>
+        <v>77.71210000000001</v>
       </c>
     </row>
     <row r="29">
@@ -30048,13 +32112,13 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>9500</v>
+        <v>8900</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>7000</v>
+        <v>6500</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>13500</v>
+        <v>12000</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
@@ -30093,17 +32157,17 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>9500</v>
+        <v>10200</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>7000</v>
+        <v>7500</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>13500</v>
+        <v>14200</v>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Mid-Segment</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="I30" s="4" t="n">
@@ -30183,17 +32247,17 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>9500</v>
+        <v>9800</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>7000</v>
+        <v>7200</v>
       </c>
       <c r="G32" s="4" t="n">
         <v>13500</v>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Mid-Segment</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="I32" s="4" t="n">
@@ -30273,13 +32337,13 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>8200</v>
+        <v>8500</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>6000</v>
+        <v>6200</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>11500</v>
+        <v>11800</v>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
@@ -30290,10 +32354,10 @@
         <v>15</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>12.9406</v>
+        <v>12.9535</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>77.7469</v>
+        <v>77.74550000000001</v>
       </c>
     </row>
     <row r="35">
@@ -30318,13 +32382,13 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>8200</v>
+        <v>8100</v>
       </c>
       <c r="F35" s="4" t="n">
         <v>6000</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>11500</v>
+        <v>11200</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
@@ -30335,10 +32399,10 @@
         <v>11</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>12.9406</v>
+        <v>12.9288</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>77.7469</v>
+        <v>77.74509999999999</v>
       </c>
     </row>
     <row r="36">
@@ -30363,13 +32427,13 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>8200</v>
+        <v>8500</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>6000</v>
+        <v>6200</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>11500</v>
+        <v>11800</v>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
@@ -30380,10 +32444,10 @@
         <v>7</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>12.9406</v>
+        <v>12.9535</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>77.7469</v>
+        <v>77.74550000000001</v>
       </c>
     </row>
     <row r="37">
@@ -44957,7 +47021,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>KR Puram–Mahadevapura, Varthur–Gunjur, Budigere Cross–OMR East</t>
+          <t>Varthur–Gunjur, Budigere Cross–OMR East, KR Puram–Mahadevapura</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -45047,7 +47111,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>KR Puram–Mahadevapura, Varthur–Gunjur, Budigere Cross–OMR East</t>
+          <t>Varthur–Gunjur, Budigere Cross–OMR East, KR Puram–Mahadevapura</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -45137,7 +47201,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>KR Puram–Mahadevapura, Budigere Cross–OMR East</t>
+          <t>Budigere Cross–OMR East, KR Puram–Mahadevapura</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -45257,7 +47321,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>KR Puram–Mahadevapura, Budigere Cross–OMR East</t>
+          <t>Budigere Cross–OMR East, KR Puram–Mahadevapura</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -45497,7 +47561,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>KR Puram–Mahadevapura, Varthur–Gunjur, Core Whitefield–Hoodi</t>
+          <t>Varthur–Gunjur, KR Puram–Mahadevapura, Core Whitefield–Hoodi</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -45557,7 +47621,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Core Whitefield–Hoodi, Budigere Cross–OMR East</t>
+          <t>Budigere Cross–OMR East, Core Whitefield–Hoodi</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -45587,7 +47651,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>KR Puram–Mahadevapura, Varthur–Gunjur, Budigere Cross–OMR East</t>
+          <t>Varthur–Gunjur, Budigere Cross–OMR East, KR Puram–Mahadevapura</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -45617,7 +47681,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>KR Puram–Mahadevapura, Budigere Cross–OMR East</t>
+          <t>Budigere Cross–OMR East, KR Puram–Mahadevapura</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -45792,7 +47856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -46009,27 +48073,27 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>AP08</t>
+          <t>AP04</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Indiranagar</t>
+          <t>Richmond Town</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>East Bangalore</t>
+          <t>Central Bangalore</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>17500</v>
+        <v>21500</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>13000</v>
+        <v>16000</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>24000</v>
+        <v>28000</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -46037,14 +48101,14 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>12.9784</v>
+        <v>12.9612</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>77.6408</v>
+        <v>77.60120000000001</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Ultra-luxury pricing backed by commercial high-street proximity, central location, and legacy residential prestige.</t>
+          <t>Prime central location with land scarcity, walk-to-work commercial centers, and premier social infrastructure.</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -46056,27 +48120,27 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>AP10</t>
+          <t>AP05</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Koramangala</t>
+          <t>Sadashivanagar</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>East Bangalore</t>
+          <t>Central Bangalore</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>16500</v>
+        <v>24000</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>12000</v>
+        <v>18000</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>23000</v>
+        <v>32000</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -46084,14 +48148,14 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>12.9352</v>
+        <v>13.0082</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>77.6245</v>
+        <v>77.5812</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Premium pricing driven by startup ecosystem density, central position, and mature social amenities.</t>
+          <t>Prime central location with land scarcity, walk-to-work commercial centers, and premier social infrastructure.</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -46103,12 +48167,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>AP21</t>
+          <t>AP06</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Hebbal</t>
+          <t>Dollars Colony</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -46117,92 +48181,92 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>11800</v>
+        <v>18500</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>8500</v>
+        <v>14000</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>17000</v>
+        <v>25000</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>Ultra-Luxury</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>13.0358</v>
+        <v>13.0282</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>77.59699999999999</v>
+        <v>77.5782</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>North Bengaluru gateway location with direct Elevated Airport Expressway and lakefront luxury projects.</t>
+          <t>Prime central location with land scarcity, walk-to-work commercial centers, and premier social infrastructure.</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Operational Metro Line Access, High Tech Hub Proximity, Proven Builder Appreciation Track Record</t>
+          <t>Central Prime Connectivity, High Secondary Resale Liquidity, Land Scarcity &amp; Prestige Address</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>AP22</t>
+          <t>AP07</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Bellandur</t>
+          <t>Sankey Road / Golf Course</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>East Bangalore</t>
+          <t>Central Bangalore</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>11500</v>
+        <v>26000</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>8500</v>
+        <v>20000</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>16000</v>
+        <v>35000</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>Ultra-Luxury</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>12.9304</v>
+        <v>12.9982</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>77.6784</v>
+        <v>77.5812</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Established tech corridor with operational metro lines, Grade-A builder projects, and mature schools/hospitals.</t>
+          <t>Prime central location with land scarcity, walk-to-work commercial centers, and premier social infrastructure.</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Operational Metro Line Access, High Tech Hub Proximity, Proven Builder Appreciation Track Record</t>
+          <t>Central Prime Connectivity, High Secondary Resale Liquidity, Land Scarcity &amp; Prestige Address</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>AP28</t>
+          <t>AP08</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Whitefield</t>
+          <t>Indiranagar</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -46211,45 +48275,45 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>10500</v>
+        <v>17500</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>7500</v>
+        <v>13000</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>15000</v>
+        <v>24000</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>Ultra-Luxury</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>12.9698</v>
+        <v>12.9784</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>77.7499</v>
+        <v>77.6408</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Priced for operational Purple Line Metro, walk-to-work ITPL access, and proven secondary market resale demand.</t>
+          <t>Ultra-luxury pricing backed by commercial high-street proximity, central location, and legacy residential prestige.</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Operational Metro Line Access, High Tech Hub Proximity, Proven Builder Appreciation Track Record</t>
+          <t>Central Prime Connectivity, High Secondary Resale Liquidity, Land Scarcity &amp; Prestige Address</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>AP30</t>
+          <t>AP09</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Brookefield</t>
+          <t>Defence Colony Indiranagar</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -46258,45 +48322,45 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>10200</v>
+        <v>19000</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>7800</v>
+        <v>14500</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>14000</v>
+        <v>26000</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>Ultra-Luxury</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>12.9657</v>
+        <v>12.9721</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>77.71850000000001</v>
+        <v>77.6452</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>High demand driven by Kundalahalli Metro stop, mature residential layout, and limited land for new launches.</t>
+          <t>Prime central location with land scarcity, walk-to-work commercial centers, and premier social infrastructure.</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Operational Metro Line Access, High Tech Hub Proximity, Proven Builder Appreciation Track Record</t>
+          <t>Central Prime Connectivity, High Secondary Resale Liquidity, Land Scarcity &amp; Prestige Address</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>AP38</t>
+          <t>AP10</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Sarjapur Road</t>
+          <t>Koramangala</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -46305,45 +48369,45 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>9500</v>
+        <v>16500</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>6800</v>
+        <v>12000</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>13500</v>
+        <v>23000</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Mid-Segment</t>
+          <t>Ultra-Luxury</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>12.9087</v>
+        <v>12.9352</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>77.6871</v>
+        <v>77.6245</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Rapidly growing corridor benefiting from upcoming metro extensions, master-planned townships, and strong entry value.</t>
+          <t>Premium pricing driven by startup ecosystem density, central position, and mature social amenities.</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Upcoming Infrastructure &amp; Metro, Township Living &amp; Greenery, Strong 3-5 Yr Appreciation Potential</t>
+          <t>Central Prime Connectivity, High Secondary Resale Liquidity, Land Scarcity &amp; Prestige Address</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>AP40</t>
+          <t>AP11</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Marathahalli</t>
+          <t>Koramangala 3rd &amp; 4th Block</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -46352,45 +48416,45 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>9200</v>
+        <v>18000</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>6800</v>
+        <v>13500</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>12500</v>
+        <v>25000</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Mid-Segment</t>
+          <t>Ultra-Luxury</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>12.9592</v>
+        <v>12.9341</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>77.6974</v>
+        <v>77.6251</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Rapidly growing corridor benefiting from upcoming metro extensions, master-planned townships, and strong entry value.</t>
+          <t>Prime central location with land scarcity, walk-to-work commercial centers, and premier social infrastructure.</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Upcoming Infrastructure &amp; Metro, Township Living &amp; Greenery, Strong 3-5 Yr Appreciation Potential</t>
+          <t>Central Prime Connectivity, High Secondary Resale Liquidity, Land Scarcity &amp; Prestige Address</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>AP47</t>
+          <t>AP12</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Mahadevapura</t>
+          <t>Ulsoor / Cambridge Layout</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -46399,219 +48463,2475 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>8500</v>
+        <v>15500</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>6200</v>
+        <v>11500</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>11800</v>
+        <v>21000</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Mid-Segment</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>12.9902</v>
+        <v>12.9752</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>77.6953</v>
+        <v>77.62520000000001</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Rapidly growing corridor benefiting from upcoming metro extensions, master-planned townships, and strong entry value.</t>
+          <t>Established tech corridor with operational metro lines, Grade-A builder projects, and mature schools/hospitals.</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Upcoming Infrastructure &amp; Metro, Township Living &amp; Greenery, Strong 3-5 Yr Appreciation Potential</t>
+          <t>Operational Metro Line Access, High Tech Hub Proximity, Proven Builder Appreciation Track Record</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>AP52</t>
+          <t>AP13</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Varthur</t>
+          <t>Benson Town</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>East Bangalore</t>
+          <t>Central Bangalore</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>8200</v>
+        <v>15000</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>6000</v>
+        <v>11000</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>11500</v>
+        <v>20000</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Mid-Segment</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>12.9406</v>
+        <v>13.0012</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>77.7469</v>
+        <v>77.59820000000001</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Priced at mid-segment entry with high upside due to Varthur Lakefront rejuvenation and ITPL-Sarjapur corridor status.</t>
+          <t>Established tech corridor with operational metro lines, Grade-A builder projects, and mature schools/hospitals.</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Upcoming Infrastructure &amp; Metro, Township Living &amp; Greenery, Strong 3-5 Yr Appreciation Potential</t>
+          <t>Operational Metro Line Access, High Tech Hub Proximity, Proven Builder Appreciation Track Record</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>AP56</t>
+          <t>AP14</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Budigere Cross</t>
+          <t>Frazer Town / Pulakeshinagar</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>East Bangalore</t>
+          <t>Central Bangalore</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>7500</v>
+        <v>14500</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>5600</v>
+        <v>10500</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>10200</v>
+        <v>19500</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Mid-Segment</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>13.0673</v>
+        <v>12.9982</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>77.7423</v>
+        <v>77.6082</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Strategic 8-lane road access to Airport and OMR; high township development momentum driving appreciation.</t>
+          <t>Established tech corridor with operational metro lines, Grade-A builder projects, and mature schools/hospitals.</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Upcoming Infrastructure &amp; Metro, Township Living &amp; Greenery, Strong 3-5 Yr Appreciation Potential</t>
+          <t>Operational Metro Line Access, High Tech Hub Proximity, Proven Builder Appreciation Track Record</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>AP63</t>
+          <t>AP15</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>KR Puram</t>
+          <t>Cooke Town</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>East Bangalore</t>
+          <t>Central Bangalore</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>6800</v>
+        <v>14000</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>4800</v>
+        <v>10000</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>9200</v>
+        <v>19000</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Budget</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>13.0075</v>
+        <v>13.0012</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>77.69589999999999</v>
+        <v>77.6182</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>Arterial interchange of ORR, OMR, and Purple/Blue line metro; high rental demand from ORR tech workforce.</t>
+          <t>Established tech corridor with operational metro lines, Grade-A builder projects, and mature schools/hospitals.</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Affordable Entry Sqft Price, High Rental Yield Potential, Arterial Road &amp; Transit Growth</t>
+          <t>Operational Metro Line Access, High Tech Hub Proximity, Proven Builder Appreciation Track Record</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>AP16</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Vasanthnagar</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Central Bangalore</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>19500</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>14500</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>26000</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Ultra-Luxury</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>12.9912</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>77.5882</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Prime central location with land scarcity, walk-to-work commercial centers, and premier social infrastructure.</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Central Prime Connectivity, High Secondary Resale Liquidity, Land Scarcity &amp; Prestige Address</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>AP17</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Cunningham Road</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Central Bangalore</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>21000</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>15500</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>28000</v>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Ultra-Luxury</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>12.9882</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>77.59520000000001</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>Prime central location with land scarcity, walk-to-work commercial centers, and premier social infrastructure.</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Central Prime Connectivity, High Secondary Resale Liquidity, Land Scarcity &amp; Prestige Address</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>AP18</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Palace Road</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Central Bangalore</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>27000</v>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Ultra-Luxury</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>12.9882</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>77.5852</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Prime central location with land scarcity, walk-to-work commercial centers, and premier social infrastructure.</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Central Prime Connectivity, High Secondary Resale Liquidity, Land Scarcity &amp; Prestige Address</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>AP19</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Malleshwaram</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>West Bangalore</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>15500</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>11500</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>21000</v>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>12.9982</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>77.5682</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>Established tech corridor with operational metro lines, Grade-A builder projects, and mature schools/hospitals.</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Operational Metro Line Access, High Tech Hub Proximity, Proven Builder Appreciation Track Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>AP20</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Rajajinagar</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>West Bangalore</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>13500</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>18500</v>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>12.9912</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>77.5532</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>Established tech corridor with operational metro lines, Grade-A builder projects, and mature schools/hospitals.</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Operational Metro Line Access, High Tech Hub Proximity, Proven Builder Appreciation Track Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>AP21</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Hebbal</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>North Bangalore</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>11800</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>8500</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>17000</v>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>13.0358</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>77.59699999999999</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>North Bengaluru gateway location with direct Elevated Airport Expressway and lakefront luxury projects.</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Operational Metro Line Access, High Tech Hub Proximity, Proven Builder Appreciation Track Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>AP22</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Bellandur</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>11500</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>8500</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>16000</v>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>12.9304</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>77.6784</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>Established tech corridor with operational metro lines, Grade-A builder projects, and mature schools/hospitals.</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Operational Metro Line Access, High Tech Hub Proximity, Proven Builder Appreciation Track Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>AP23</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Devarabesanahalli / ORR</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>12200</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>16500</v>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>12.9298</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>77.6862</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>Established tech corridor with operational metro lines, Grade-A builder projects, and mature schools/hospitals.</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Operational Metro Line Access, High Tech Hub Proximity, Proven Builder Appreciation Track Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>AP24</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Kadubeesanahalli / ORR</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>8800</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>16200</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>12.9366</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>77.69199999999999</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>Established tech corridor with operational metro lines, Grade-A builder projects, and mature schools/hospitals.</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Operational Metro Line Access, High Tech Hub Proximity, Proven Builder Appreciation Track Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>AP25</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Marathahalli - Sarjapur ORR</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>11800</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>8600</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>16000</v>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>12.9305</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>77.6874</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>Established tech corridor with operational metro lines, Grade-A builder projects, and mature schools/hospitals.</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Operational Metro Line Access, High Tech Hub Proximity, Proven Builder Appreciation Track Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>AP26</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>HSR Layout</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>South Bangalore</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>13000</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>9500</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>17500</v>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>12.9121</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>77.64449999999999</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>Established tech corridor with operational metro lines, Grade-A builder projects, and mature schools/hospitals.</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Operational Metro Line Access, High Tech Hub Proximity, Proven Builder Appreciation Track Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>AP27</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Jayanagar</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>South Bangalore</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>14000</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>10200</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>19000</v>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>12.9282</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>77.58320000000001</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>Established tech corridor with operational metro lines, Grade-A builder projects, and mature schools/hospitals.</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Operational Metro Line Access, High Tech Hub Proximity, Proven Builder Appreciation Track Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>AP28</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Whitefield</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>10500</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>7500</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>12.9698</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>77.7499</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>Priced for operational Purple Line Metro, walk-to-work ITPL access, and proven secondary market resale demand.</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Operational Metro Line Access, High Tech Hub Proximity, Proven Builder Appreciation Track Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>AP29</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>EPIP Zone Whitefield</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>11200</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>8200</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>15500</v>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>12.9758</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>77.7248</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>Established tech corridor with operational metro lines, Grade-A builder projects, and mature schools/hospitals.</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Operational Metro Line Access, High Tech Hub Proximity, Proven Builder Appreciation Track Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>AP30</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Brookefield</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>10200</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>7800</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>14000</v>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>12.9657</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>77.71850000000001</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>High demand driven by Kundalahalli Metro stop, mature residential layout, and limited land for new launches.</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Operational Metro Line Access, High Tech Hub Proximity, Proven Builder Appreciation Track Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>AP31</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Kundalahalli</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>7500</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>13800</v>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>12.9658</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>77.7115</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>Established tech corridor with operational metro lines, Grade-A builder projects, and mature schools/hospitals.</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Operational Metro Line Access, High Tech Hub Proximity, Proven Builder Appreciation Track Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>AP32</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Siddapura / Nallurhalli</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>9800</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>7200</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>13500</v>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>12.9619</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>77.7291</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>Established tech corridor with operational metro lines, Grade-A builder projects, and mature schools/hospitals.</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Operational Metro Line Access, High Tech Hub Proximity, Proven Builder Appreciation Track Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>AP33</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>ECC Road Whitefield</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>15200</v>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>12.978</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>77.73779999999999</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>Established tech corridor with operational metro lines, Grade-A builder projects, and mature schools/hospitals.</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Operational Metro Line Access, High Tech Hub Proximity, Proven Builder Appreciation Track Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>AP34</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Hope Farm Junction</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>10400</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>7600</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>14500</v>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>12.9858</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>77.74890000000001</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>Established tech corridor with operational metro lines, Grade-A builder projects, and mature schools/hospitals.</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Operational Metro Line Access, High Tech Hub Proximity, Proven Builder Appreciation Track Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>AP35</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Pattandur Agrahara</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>10200</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>7500</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>14200</v>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>12.9873</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>77.7531</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>Established tech corridor with operational metro lines, Grade-A builder projects, and mature schools/hospitals.</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Operational Metro Line Access, High Tech Hub Proximity, Proven Builder Appreciation Track Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>AP36</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Kadugodi</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>9500</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>13000</v>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Mid-Segment</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>12.9892</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>77.7508</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>Rapidly growing corridor benefiting from upcoming metro extensions, master-planned townships, and strong entry value.</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Upcoming Infrastructure &amp; Metro, Township Living &amp; Greenery, Strong 3-5 Yr Appreciation Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>AP37</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Belathur</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>8800</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>12200</v>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Mid-Segment</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>13.0117</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>77.74590000000001</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>Rapidly growing corridor benefiting from upcoming metro extensions, master-planned townships, and strong entry value.</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Upcoming Infrastructure &amp; Metro, Township Living &amp; Greenery, Strong 3-5 Yr Appreciation Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>AP38</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Sarjapur Road</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>9500</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>6800</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>13500</v>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Mid-Segment</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>12.9087</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>77.6871</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>Rapidly growing corridor benefiting from upcoming metro extensions, master-planned townships, and strong entry value.</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Upcoming Infrastructure &amp; Metro, Township Living &amp; Greenery, Strong 3-5 Yr Appreciation Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>AP39</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Doddakannelli / Haralur</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>9800</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>13800</v>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Mid-Segment</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>12.9094</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>77.6978</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>Rapidly growing corridor benefiting from upcoming metro extensions, master-planned townships, and strong entry value.</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Upcoming Infrastructure &amp; Metro, Township Living &amp; Greenery, Strong 3-5 Yr Appreciation Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>AP40</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Marathahalli</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>9200</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>6800</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>12500</v>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>Mid-Segment</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>12.9592</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>77.6974</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>Rapidly growing corridor benefiting from upcoming metro extensions, master-planned townships, and strong entry value.</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Upcoming Infrastructure &amp; Metro, Township Living &amp; Greenery, Strong 3-5 Yr Appreciation Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>AP41</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Doddanekundi</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>6600</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>12200</v>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Mid-Segment</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>12.9728</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>77.6961</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>Rapidly growing corridor benefiting from upcoming metro extensions, master-planned townships, and strong entry value.</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Upcoming Infrastructure &amp; Metro, Township Living &amp; Greenery, Strong 3-5 Yr Appreciation Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>AP42</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Panathur</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>8900</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Mid-Segment</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>12.9348</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>77.71210000000001</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>Rapidly growing corridor benefiting from upcoming metro extensions, master-planned townships, and strong entry value.</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Upcoming Infrastructure &amp; Metro, Township Living &amp; Greenery, Strong 3-5 Yr Appreciation Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>AP43</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Balagere</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>6200</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>11500</v>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Mid-Segment</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>12.9308</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>77.7192</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>Rapidly growing corridor benefiting from upcoming metro extensions, master-planned townships, and strong entry value.</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>Upcoming Infrastructure &amp; Metro, Township Living &amp; Greenery, Strong 3-5 Yr Appreciation Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>AP44</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Gunjur</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>8100</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>11200</v>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Mid-Segment</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>12.9288</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>77.74509999999999</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>Rapidly growing corridor benefiting from upcoming metro extensions, master-planned townships, and strong entry value.</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Upcoming Infrastructure &amp; Metro, Township Living &amp; Greenery, Strong 3-5 Yr Appreciation Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>AP45</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Soukya Road</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>7800</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>10800</v>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Mid-Segment</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>12.9621</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>77.7698</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>Rapidly growing corridor benefiting from upcoming metro extensions, master-planned townships, and strong entry value.</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Upcoming Infrastructure &amp; Metro, Township Living &amp; Greenery, Strong 3-5 Yr Appreciation Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>AP46</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Seetharamapalya</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>8900</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Mid-Segment</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>12.9781</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>77.7058</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>Rapidly growing corridor benefiting from upcoming metro extensions, master-planned townships, and strong entry value.</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Upcoming Infrastructure &amp; Metro, Township Living &amp; Greenery, Strong 3-5 Yr Appreciation Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>AP47</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Mahadevapura</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>8500</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>6200</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>11800</v>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Mid-Segment</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>12.9902</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>77.6953</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>Rapidly growing corridor benefiting from upcoming metro extensions, master-planned townships, and strong entry value.</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>Upcoming Infrastructure &amp; Metro, Township Living &amp; Greenery, Strong 3-5 Yr Appreciation Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>AP48</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Hoodi</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>8700</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>6400</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>11900</v>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>Mid-Segment</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>12.9868</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>77.7011</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>Rapidly growing corridor benefiting from upcoming metro extensions, master-planned townships, and strong entry value.</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Upcoming Infrastructure &amp; Metro, Township Living &amp; Greenery, Strong 3-5 Yr Appreciation Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>AP49</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Garudacharpalya</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>6100</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>11500</v>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Mid-Segment</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>12.9904</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>77.6961</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>Rapidly growing corridor benefiting from upcoming metro extensions, master-planned townships, and strong entry value.</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>Upcoming Infrastructure &amp; Metro, Township Living &amp; Greenery, Strong 3-5 Yr Appreciation Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>AP50</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Singayyanapalya</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>8300</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>11400</v>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>Mid-Segment</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>12.9912</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>77.6871</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>Rapidly growing corridor benefiting from upcoming metro extensions, master-planned townships, and strong entry value.</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>Upcoming Infrastructure &amp; Metro, Township Living &amp; Greenery, Strong 3-5 Yr Appreciation Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>AP51</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Varthur Junction</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>8500</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>6200</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>11800</v>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Mid-Segment</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>12.9535</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>77.74550000000001</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>Rapidly growing corridor benefiting from upcoming metro extensions, master-planned townships, and strong entry value.</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>Upcoming Infrastructure &amp; Metro, Township Living &amp; Greenery, Strong 3-5 Yr Appreciation Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>AP52</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Varthur</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>8200</v>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>11500</v>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>Mid-Segment</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>12.9406</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>77.7469</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>Priced at mid-segment entry with high upside due to Varthur Lakefront rejuvenation and ITPL-Sarjapur corridor status.</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>Upcoming Infrastructure &amp; Metro, Township Living &amp; Greenery, Strong 3-5 Yr Appreciation Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>AP53</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Varthur Lakefront</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>8600</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>6300</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>11900</v>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>Mid-Segment</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>12.9421</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>77.74120000000001</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>Rapidly growing corridor benefiting from upcoming metro extensions, master-planned townships, and strong entry value.</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>Upcoming Infrastructure &amp; Metro, Township Living &amp; Greenery, Strong 3-5 Yr Appreciation Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>AP54</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Cheemasandra</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>7600</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>5600</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>10400</v>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>Mid-Segment</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>13.0496</v>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>77.7475</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>Rapidly growing corridor benefiting from upcoming metro extensions, master-planned townships, and strong entry value.</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>Upcoming Infrastructure &amp; Metro, Township Living &amp; Greenery, Strong 3-5 Yr Appreciation Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>AP55</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Nimbekaipura</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>7400</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>Mid-Segment</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>13.0561</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>77.7512</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>Rapidly growing corridor benefiting from upcoming metro extensions, master-planned townships, and strong entry value.</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>Upcoming Infrastructure &amp; Metro, Township Living &amp; Greenery, Strong 3-5 Yr Appreciation Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>AP56</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Budigere Cross</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>5600</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>10200</v>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>Mid-Segment</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>13.0673</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>77.7423</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>Strategic 8-lane road access to Airport and OMR; high township development momentum driving appreciation.</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>Upcoming Infrastructure &amp; Metro, Township Living &amp; Greenery, Strong 3-5 Yr Appreciation Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>AP57</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Budigere Main Road</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>7300</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>5400</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>9900</v>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Mid-Segment</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>13.0512</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>77.74809999999999</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>Rapidly growing corridor benefiting from upcoming metro extensions, master-planned townships, and strong entry value.</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>Upcoming Infrastructure &amp; Metro, Township Living &amp; Greenery, Strong 3-5 Yr Appreciation Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>AP58</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Mandur / Budigere</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>7100</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>5200</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>9600</v>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>Mid-Segment</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>13.0712</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>77.7495</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>Rapidly growing corridor benefiting from upcoming metro extensions, master-planned townships, and strong entry value.</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>Upcoming Infrastructure &amp; Metro, Township Living &amp; Greenery, Strong 3-5 Yr Appreciation Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>AP59</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Hoskote Toll / OMR</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>6900</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>9400</v>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>13.0612</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>77.76819999999999</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>Emerging arterial connectivity hub offering affordable entry price points, high rental yields, and upcoming road upgrades.</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>Affordable Entry Sqft Price, High Rental Yield Potential, Arterial Road &amp; Transit Growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>AP60</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Aavalahalli</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>7000</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>5100</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>9500</v>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>13.0231</v>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>77.7118</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>Emerging arterial connectivity hub offering affordable entry price points, high rental yields, and upcoming road upgrades.</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>Affordable Entry Sqft Price, High Rental Yield Potential, Arterial Road &amp; Transit Growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>AP61</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Battarahalli</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>7200</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>5300</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>9800</v>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>13.0145</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>77.7012</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>Emerging arterial connectivity hub offering affordable entry price points, high rental yields, and upcoming road upgrades.</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>Affordable Entry Sqft Price, High Rental Yield Potential, Arterial Road &amp; Transit Growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>AP62</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Benniganahalli</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>7800</v>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>5700</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>10500</v>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>Mid-Segment</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="n">
+        <v>12.9935</v>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>77.66200000000001</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>Rapidly growing corridor benefiting from upcoming metro extensions, master-planned townships, and strong entry value.</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>Upcoming Infrastructure &amp; Metro, Township Living &amp; Greenery, Strong 3-5 Yr Appreciation Potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>AP63</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>KR Puram</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>East Bangalore</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>6800</v>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>4800</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>9200</v>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="n">
+        <v>13.0075</v>
+      </c>
+      <c r="I64" s="4" t="n">
+        <v>77.69589999999999</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>Arterial interchange of ORR, OMR, and Purple/Blue line metro; high rental demand from ORR tech workforce.</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>Affordable Entry Sqft Price, High Rental Yield Potential, Arterial Road &amp; Transit Growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
           <t>AP64</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>Electronic City Phase 1</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>South Bangalore</t>
         </is>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D65" s="4" t="n">
         <v>6800</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E65" s="4" t="n">
         <v>5000</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F65" s="4" t="n">
         <v>9200</v>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G65" s="3" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="H65" s="4" t="n">
         <v>12.8452</v>
       </c>
-      <c r="I17" s="4" t="n">
+      <c r="I65" s="4" t="n">
         <v>77.6602</v>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="J65" s="3" t="inlineStr">
         <is>
           <t>Emerging arterial connectivity hub offering affordable entry price points, high rental yields, and upcoming road upgrades.</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="K65" s="3" t="inlineStr">
         <is>
           <t>Affordable Entry Sqft Price, High Rental Yield Potential, Arterial Road &amp; Transit Growth</t>
         </is>
